--- a/backend/data/excel/65d3a980d932_data.xlsx
+++ b/backend/data/excel/65d3a980d932_data.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-09-22 09:32:41</t>
+          <t>2025-09-22 10:22:04</t>
         </is>
       </c>
     </row>

--- a/backend/data/excel/65d3a980d932_data.xlsx
+++ b/backend/data/excel/65d3a980d932_data.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-09-22 18:20:33</t>
+          <t>2025-09-23 10:57:57</t>
         </is>
       </c>
     </row>

--- a/backend/data/excel/65d3a980d932_data.xlsx
+++ b/backend/data/excel/65d3a980d932_data.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-10-14 10:06:30</t>
+          <t>2025-10-14 23:58:13</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-14   10:00</t>
+          <t>다운로드 시간 : 2025-10-14   23:55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -75449,7 +75449,7 @@
       <c r="H1735" t="inlineStr"/>
       <c r="I1735" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-14   10:03</t>
+          <t>다운로드 시간 : 2025-10-14   23:56</t>
         </is>
       </c>
       <c r="J1735" t="inlineStr"/>
@@ -80761,7 +80761,7 @@
       <c r="I1872" t="inlineStr"/>
       <c r="J1872" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-14   10:05</t>
+          <t>다운로드 시간 : 2025-10-14   23:57</t>
         </is>
       </c>
       <c r="K1872" t="inlineStr"/>
@@ -80886,7 +80886,7 @@
       <c r="J1876" t="inlineStr"/>
       <c r="K1876" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-14   10:06</t>
+          <t>다운로드 시간 : 2025-10-14   23:58</t>
         </is>
       </c>
     </row>
